--- a/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -19988,7 +19988,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20407,7 +20407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -19988,7 +19988,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20407,7 +20407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:29 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -19988,7 +19988,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20407,7 +20407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:33 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -19988,7 +19988,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20407,7 +20407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:36 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -19988,7 +19988,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20407,7 +20407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 02:50 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -19988,7 +19988,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20407,7 +20407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:02 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -19988,7 +19988,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20407,7 +20407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:11 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -19988,7 +19988,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20407,7 +20407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:14 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -19988,7 +19988,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20407,7 +20407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:17 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -19988,7 +19988,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20407,7 +20407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:24 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19988,7 +19988,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -20407,7 +20407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14049,14 +14049,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B2B Opaco · Top 100 corp · ordenado por CR únicos ↓</t>
+          <t>B2B Opaco · Top 100 corp · ordenado por Eficacia ↑ (menor a mayor)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14118,37 +14118,37 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>IHG</t>
+          <t>Station Casinos</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, Expedia, Internal</t>
+          <t>HBSI</t>
         </is>
       </c>
       <c r="D6" s="12" t="n">
-        <v>400627</v>
+        <v>264</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>368176</v>
+        <v>0</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>5169</v>
+        <v>0</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>0.9189994683333874</v>
+        <v>0</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>0.01290227568286711</v>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -14158,37 +14158,37 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Melia</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, HBSI, Internal</t>
+          <t>HBSI</t>
         </is>
       </c>
       <c r="D7" s="12" t="n">
-        <v>282969</v>
+        <v>2447</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>274819</v>
+        <v>1694</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>2891</v>
+        <v>4</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>0.9711982584664751</v>
+        <v>0.6922762566407846</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>0.01021666684336447</v>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.001634654679199019</v>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14198,37 +14198,37 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Hyatt</t>
+          <t>Caesars Entertainment</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>HBSI</t>
         </is>
       </c>
       <c r="D8" s="12" t="n">
-        <v>186534</v>
+        <v>34517</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>177719</v>
+        <v>28448</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1975</v>
+        <v>244</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>0.9527431996311664</v>
+        <v>0.8241735956195498</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>0.01058788210192244</v>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>0.007068980502361155</v>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14278,37 +14278,37 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Accor</t>
+          <t>Universal</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, Expedia, HotelBeds Apitude, Internal, SynXis</t>
+          <t>DerbySoft</t>
         </is>
       </c>
       <c r="D10" s="12" t="n">
-        <v>40160</v>
+        <v>4604</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>37812</v>
+        <v>4003</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>0.9415338645418326</v>
+        <v>0.8694613379669852</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>0.002041832669322709</v>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>0.008036490008688097</v>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -14318,37 +14318,37 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Caesars Entertainment</t>
+          <t>Royalton Hotels &amp; Resorts</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>SynXis</t>
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>34517</v>
+        <v>1549</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>28448</v>
+        <v>1395</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>244</v>
+        <v>24</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>0.8241735956195498</v>
+        <v>0.9005810200129115</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>0.007068980502361155</v>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>0.01549386701097482</v>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -14358,37 +14358,37 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Wyndham</t>
+          <t>Americas Hotels Group</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, Internal</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D12" s="12" t="n">
-        <v>23571</v>
+        <v>811</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>22064</v>
+        <v>739</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>0.9360655042212889</v>
+        <v>0.9112207151664612</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>0.004030376309872301</v>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>0.03205918618988902</v>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -14398,37 +14398,37 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>MGM Resorts</t>
+          <t>Dann</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>22113</v>
+        <v>727</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>21753</v>
+        <v>665</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>348</v>
+        <v>7</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>0.9837199837199837</v>
+        <v>0.9147180192572214</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>0.01573734907068241</v>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.009628610729023384</v>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Aceptable</t>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -14438,37 +14438,37 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Marriott</t>
+          <t>IHG</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Expedia, Internal</t>
+          <t>DerbySoft, Expedia, Internal</t>
         </is>
       </c>
       <c r="D14" s="12" t="n">
-        <v>21823</v>
+        <v>400627</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>21207</v>
+        <v>368176</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>28</v>
+        <v>5169</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>0.9717729001512166</v>
+        <v>0.9189994683333874</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>0.001283049993126518</v>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.01290227568286711</v>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -14478,37 +14478,37 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Hyatt Inclusive Collection</t>
+          <t>Barcelo</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>SynXis</t>
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>15461</v>
+        <v>8075</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>15376</v>
+        <v>7437</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.9945022960998642</v>
+        <v>0.9209907120743034</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>0.008925683979044046</v>
-      </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.01535603715170279</v>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -14518,28 +14518,28 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Barcelo</t>
+          <t>Presidente Intercontinental</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>SynXis</t>
+          <t>DerbySoft</t>
         </is>
       </c>
       <c r="D16" s="12" t="n">
-        <v>8075</v>
+        <v>2310</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>7437</v>
+        <v>2131</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>0.9209907120743034</v>
+        <v>0.9225108225108225</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>0.01535603715170279</v>
+        <v>0.01818181818181818</v>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
@@ -14598,37 +14598,37 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Palladium Hotel Group</t>
+          <t>Wyndham</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Siteminder</t>
+          <t>DerbySoft, Internal</t>
         </is>
       </c>
       <c r="D18" s="12" t="n">
-        <v>7602</v>
+        <v>23571</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>7602</v>
+        <v>22064</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>486</v>
+        <v>95</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>1</v>
+        <v>0.9360655042212889</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>0.06393054459352802</v>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.004030376309872301</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Exitosa</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14638,32 +14638,32 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Disney</t>
+          <t>Accor</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>DerbySoft, Expedia, HotelBeds Apitude, Internal, SynXis</t>
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>7551</v>
+        <v>40160</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>7506</v>
+        <v>37812</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>0.9940405244338498</v>
+        <v>0.9415338645418326</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>0.003972983710766786</v>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.002041832669322709</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -14678,32 +14678,32 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>PAM Hotels</t>
+          <t>Karisma</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Internal, SynXis</t>
+          <t>SynXis</t>
         </is>
       </c>
       <c r="D20" s="12" t="n">
-        <v>5175</v>
+        <v>1432</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>5104</v>
+        <v>1356</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>0.986280193236715</v>
+        <v>0.946927374301676</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>0.02260869565217391</v>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.02025139664804469</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -14718,7 +14718,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Hoteles Xcaret</t>
+          <t>Hoteles Geh Suites</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -14727,28 +14727,28 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>4898</v>
+        <v>889</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>4889</v>
+        <v>845</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>0.9981625153123724</v>
+        <v>0.9505061867266592</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>0.002449979583503471</v>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.01124859392575928</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -14758,32 +14758,32 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Universal</t>
+          <t>Ocean by H10</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>4604</v>
+        <v>3481</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>4003</v>
+        <v>3311</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>0.8694613379669852</v>
+        <v>0.9511634587762138</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>0.008036490008688097</v>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0.01493823613904051</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -14798,28 +14798,28 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Krystal</t>
+          <t>Hyatt</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>DerbySoft</t>
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>3935</v>
+        <v>186534</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>3785</v>
+        <v>177719</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>55</v>
+        <v>1975</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>0.9618805590851334</v>
+        <v>0.9527431996311664</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>0.01397712833545108</v>
+        <v>0.01058788210192244</v>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Ocean by H10</t>
+          <t>Las Brisas</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -14847,19 +14847,19 @@
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>3481</v>
+        <v>1975</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>3311</v>
+        <v>1896</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>0.9511634587762138</v>
+        <v>0.96</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>0.01493823613904051</v>
+        <v>0.04455696202531646</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -14878,37 +14878,37 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>GRUPO POSADAS</t>
+          <t>CHOICE</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>DerbySoft, Expedia, Internal</t>
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>3068</v>
+        <v>1377</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>2988</v>
+        <v>1324</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>0.9739243807040417</v>
+        <v>0.9615105301379812</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>0.02183833116036506</v>
-      </c>
-      <c r="I25" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.005083514887436456</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Aceptable</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>RIU</t>
+          <t>Krystal</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -14927,28 +14927,28 @@
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>2801</v>
+        <v>3935</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>2797</v>
+        <v>3785</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>0.9985719385933595</v>
+        <v>0.9618805590851334</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>0.004284184219921457</v>
-      </c>
-      <c r="I26" s="10" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
+        <v>0.01397712833545108</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -14958,28 +14958,28 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Park Royal</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>DerbySoft, HBSI, Internal</t>
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>2766</v>
+        <v>282969</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>2716</v>
+        <v>274819</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>58</v>
+        <v>2891</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>0.9819233550253073</v>
+        <v>0.9711982584664751</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>0.02096890817064353</v>
+        <v>0.01021666684336447</v>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Aceptable</t>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -14998,32 +14998,32 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Melia</t>
+          <t>Marriott</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>Expedia, Internal</t>
         </is>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2447</v>
+        <v>21823</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>1694</v>
+        <v>21207</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>0.6922762566407846</v>
+        <v>0.9717729001512166</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>0.001634654679199019</v>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
+        <v>0.001283049993126518</v>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -15038,28 +15038,28 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Decameron</t>
+          <t>GRUPO POSADAS</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>HBSI</t>
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>2353</v>
+        <v>3068</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>2313</v>
+        <v>2988</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>155</v>
+        <v>67</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>0.9830004249893752</v>
+        <v>0.9739243807040417</v>
       </c>
       <c r="H29" s="13" t="n">
-        <v>0.06587335316617085</v>
+        <v>0.02183833116036506</v>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Exitosa</t>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -15078,37 +15078,37 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Presidente Intercontinental</t>
+          <t>Faranda Hotels</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>Siteminder</t>
         </is>
       </c>
       <c r="D30" s="12" t="n">
-        <v>2310</v>
+        <v>326</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>2131</v>
+        <v>320</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.9225108225108225</v>
+        <v>0.9815950920245399</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>0.01818181818181818</v>
-      </c>
-      <c r="I30" s="8" t="inlineStr">
+        <v>0.009202453987730062</v>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -15118,7 +15118,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Palace</t>
+          <t>Park Royal</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -15127,19 +15127,19 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>2260</v>
+        <v>2766</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>2250</v>
+        <v>2716</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>0.995575221238938</v>
+        <v>0.9819233550253073</v>
       </c>
       <c r="H31" s="13" t="n">
-        <v>0.03008849557522124</v>
+        <v>0.02096890817064353</v>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Exitosa</t>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Emporio</t>
+          <t>Bahia Principe</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -15167,19 +15167,19 @@
         </is>
       </c>
       <c r="D32" s="12" t="n">
-        <v>2198</v>
+        <v>2057</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>2183</v>
+        <v>2021</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>0.9931756141947224</v>
+        <v>0.982498784637822</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>0.0172884440400364</v>
+        <v>0.02430724355858046</v>
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
@@ -15198,28 +15198,28 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Wynn Las Vegas</t>
+          <t>GHL</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>2122</v>
+        <v>1086</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>2120</v>
+        <v>1067</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>0.9990574929311969</v>
+        <v>0.9825046040515654</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>0.008011310084825637</v>
+        <v>0.03406998158379374</v>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15238,7 +15238,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Bahia Principe</t>
+          <t>Decameron</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -15247,19 +15247,19 @@
         </is>
       </c>
       <c r="D34" s="12" t="n">
-        <v>2057</v>
+        <v>2353</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>2021</v>
+        <v>2313</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>50</v>
+        <v>155</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>0.982498784637822</v>
+        <v>0.9830004249893752</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>0.02430724355858046</v>
+        <v>0.06587335316617085</v>
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
@@ -15268,7 +15268,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Aceptable</t>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15278,37 +15278,37 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Las Brisas</t>
+          <t>MGM Resorts</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>HBSI</t>
         </is>
       </c>
       <c r="D35" s="12" t="n">
-        <v>1975</v>
+        <v>22113</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>1896</v>
+        <v>21753</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>88</v>
+        <v>348</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>0.96</v>
+        <v>0.9837199837199837</v>
       </c>
       <c r="H35" s="13" t="n">
-        <v>0.04455696202531646</v>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
+        <v>0.01573734907068241</v>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15318,32 +15318,32 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Royalton Hotels &amp; Resorts</t>
+          <t>PAM Hotels</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>SynXis</t>
+          <t>Internal, SynXis</t>
         </is>
       </c>
       <c r="D36" s="12" t="n">
-        <v>1549</v>
+        <v>5175</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>1395</v>
+        <v>5104</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0.9005810200129115</v>
+        <v>0.986280193236715</v>
       </c>
       <c r="H36" s="13" t="n">
-        <v>0.01549386701097482</v>
-      </c>
-      <c r="I36" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0.02260869565217391</v>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
@@ -15358,37 +15358,37 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Karisma</t>
+          <t>Iberostar</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>SynXis</t>
+          <t>HBSI</t>
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>1432</v>
+        <v>401</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>1356</v>
+        <v>398</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>0.946927374301676</v>
+        <v>0.9925187032418953</v>
       </c>
       <c r="H37" s="13" t="n">
-        <v>0.02025139664804469</v>
-      </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>0.004987531172069825</v>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Aceptable</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15398,37 +15398,37 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>CHOICE</t>
+          <t>Emporio</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, Expedia, Internal</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D38" s="12" t="n">
-        <v>1377</v>
+        <v>2198</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>1324</v>
+        <v>2183</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.9615105301379812</v>
+        <v>0.9931756141947224</v>
       </c>
       <c r="H38" s="13" t="n">
-        <v>0.005083514887436456</v>
-      </c>
-      <c r="I38" s="9" t="inlineStr">
+        <v>0.0172884440400364</v>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15438,28 +15438,28 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Sandos</t>
+          <t>Disney</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>DerbySoft</t>
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>1355</v>
+        <v>7551</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>1351</v>
+        <v>7506</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>0.9970479704797048</v>
+        <v>0.9940405244338498</v>
       </c>
       <c r="H39" s="13" t="n">
-        <v>0.00959409594095941</v>
+        <v>0.003972983710766786</v>
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15478,7 +15478,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Oasis</t>
+          <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -15487,19 +15487,19 @@
         </is>
       </c>
       <c r="D40" s="12" t="n">
-        <v>1319</v>
+        <v>15461</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>1319</v>
+        <v>15376</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>4</v>
+        <v>138</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>1</v>
+        <v>0.9945022960998642</v>
       </c>
       <c r="H40" s="13" t="n">
-        <v>0.003032600454890068</v>
+        <v>0.008925683979044046</v>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -15518,7 +15518,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>GHL</t>
+          <t>BH Hoteles</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -15527,19 +15527,19 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>1086</v>
+        <v>191</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>1067</v>
+        <v>190</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>0.9825046040515654</v>
+        <v>0.9947643979057592</v>
       </c>
       <c r="H41" s="13" t="n">
-        <v>0.03406998158379374</v>
+        <v>0.04712041884816754</v>
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
@@ -15558,28 +15558,28 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Camino Real</t>
+          <t>Palace</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Internal, Travelclick</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D42" s="12" t="n">
-        <v>1015</v>
+        <v>2260</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>1015</v>
+        <v>2250</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>1</v>
+        <v>0.995575221238938</v>
       </c>
       <c r="H42" s="13" t="n">
-        <v>0.06206896551724138</v>
+        <v>0.03008849557522124</v>
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Hoteles Geh Suites</t>
+          <t>Sandos</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -15607,23 +15607,23 @@
         </is>
       </c>
       <c r="D43" s="12" t="n">
-        <v>889</v>
+        <v>1355</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>845</v>
+        <v>1351</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>0.9505061867266592</v>
+        <v>0.9970479704797048</v>
       </c>
       <c r="H43" s="13" t="n">
-        <v>0.01124859392575928</v>
-      </c>
-      <c r="I43" s="9" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+        <v>0.00959409594095941</v>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
@@ -15638,7 +15638,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Americas Hotels Group</t>
+          <t>El Dorado San Andrés</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -15647,23 +15647,23 @@
         </is>
       </c>
       <c r="D44" s="12" t="n">
-        <v>811</v>
+        <v>354</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>739</v>
+        <v>353</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.9112207151664612</v>
+        <v>0.9971751412429378</v>
       </c>
       <c r="H44" s="13" t="n">
-        <v>0.03205918618988902</v>
-      </c>
-      <c r="I44" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0.02542372881355932</v>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Dann</t>
+          <t>Hoteles Xcaret</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -15687,28 +15687,28 @@
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>727</v>
+        <v>4898</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>665</v>
+        <v>4889</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0.9147180192572214</v>
+        <v>0.9981625153123724</v>
       </c>
       <c r="H45" s="13" t="n">
-        <v>0.009628610729023384</v>
-      </c>
-      <c r="I45" s="8" t="inlineStr">
-        <is>
-          <t>Revisar</t>
+        <v>0.002449979583503471</v>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15718,7 +15718,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Villa Group</t>
+          <t>RIU</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -15727,19 +15727,19 @@
         </is>
       </c>
       <c r="D46" s="12" t="n">
-        <v>475</v>
+        <v>2801</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>475</v>
+        <v>2797</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>1</v>
+        <v>0.9985719385933595</v>
       </c>
       <c r="H46" s="13" t="n">
-        <v>0.00631578947368421</v>
+        <v>0.004284184219921457</v>
       </c>
       <c r="I46" s="10" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Iberostar</t>
+          <t>Wynn Las Vegas</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -15767,19 +15767,19 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>401</v>
+        <v>2122</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>398</v>
+        <v>2120</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>0.9925187032418953</v>
+        <v>0.9990574929311969</v>
       </c>
       <c r="H47" s="13" t="n">
-        <v>0.004987531172069825</v>
+        <v>0.008011310084825637</v>
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Crítica</t>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -15798,28 +15798,28 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>El Dorado San Andrés</t>
+          <t>Palladium Hotel Group</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Siteminder</t>
         </is>
       </c>
       <c r="D48" s="12" t="n">
-        <v>354</v>
+        <v>7602</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>353</v>
+        <v>7602</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>9</v>
+        <v>486</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.9971751412429378</v>
+        <v>1</v>
       </c>
       <c r="H48" s="13" t="n">
-        <v>0.02542372881355932</v>
+        <v>0.06393054459352802</v>
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
@@ -15838,28 +15838,28 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Faranda Hotels</t>
+          <t>Camino Real</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Siteminder</t>
+          <t>Internal, Travelclick</t>
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>326</v>
+        <v>1015</v>
       </c>
       <c r="E49" s="12" t="n">
-        <v>320</v>
+        <v>1015</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>0.9815950920245399</v>
+        <v>1</v>
       </c>
       <c r="H49" s="13" t="n">
-        <v>0.009202453987730062</v>
+        <v>0.06206896551724138</v>
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -15878,28 +15878,28 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>EM Hotels</t>
+          <t>Villa Group</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Siteminder</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D50" s="12" t="n">
-        <v>303</v>
+        <v>475</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>303</v>
+        <v>475</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G50" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="13" t="n">
-        <v>0.0033003300330033</v>
+        <v>0.00631578947368421</v>
       </c>
       <c r="I50" s="10" t="inlineStr">
         <is>
@@ -15918,37 +15918,37 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Station Casinos</t>
+          <t>EM Hotels</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>Siteminder</t>
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>264</v>
+        <v>303</v>
       </c>
       <c r="E51" s="12" t="n">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>Súper Crítica</t>
+        <v>0.0033003300330033</v>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Sin Conversión</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -15998,7 +15998,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Lomas Hospitality</t>
+          <t>Oasis</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -16007,10 +16007,10 @@
         </is>
       </c>
       <c r="D53" s="12" t="n">
-        <v>242</v>
+        <v>1319</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>242</v>
+        <v>1319</v>
       </c>
       <c r="F53" s="12" t="n">
         <v>4</v>
@@ -16019,7 +16019,7 @@
         <v>1</v>
       </c>
       <c r="H53" s="13" t="n">
-        <v>0.01652892561983471</v>
+        <v>0.003032600454890068</v>
       </c>
       <c r="I53" s="10" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Aceptable</t>
+          <t>Crítica</t>
         </is>
       </c>
     </row>
@@ -16038,7 +16038,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Hoteles Movich</t>
+          <t>Lomas Hospitality</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -16047,19 +16047,19 @@
         </is>
       </c>
       <c r="D54" s="12" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G54" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H54" s="13" t="n">
-        <v>0.04583333333333333</v>
+        <v>0.01652892561983471</v>
       </c>
       <c r="I54" s="10" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>Exitosa</t>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Pueblo Bonito</t>
+          <t>Hoteles Movich</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -16087,19 +16087,19 @@
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G55" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H55" s="13" t="n">
-        <v>0.0187793427230047</v>
+        <v>0.04583333333333333</v>
       </c>
       <c r="I55" s="10" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Aceptable</t>
+          <t>Exitosa</t>
         </is>
       </c>
     </row>
@@ -16118,28 +16118,28 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Dorado Plaza</t>
+          <t>Pueblo Bonito</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Siteminder</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="D56" s="12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G56" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="13" t="n">
-        <v>0.009478672985781991</v>
+        <v>0.0187793427230047</v>
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>Revisar</t>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -16158,28 +16158,28 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>BH Hoteles</t>
+          <t>Dorado Plaza</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Siteminder</t>
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="E57" s="12" t="n">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>0.9947643979057592</v>
+        <v>1</v>
       </c>
       <c r="H57" s="13" t="n">
-        <v>0.04712041884816754</v>
+        <v>0.009478672985781991</v>
       </c>
       <c r="I57" s="10" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>Exitosa</t>
+          <t>Revisar</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19988,7 +19988,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -20407,7 +20407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:37 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19988,7 +19988,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -20407,7 +20407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:50 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 03:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19988,7 +19988,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -20407,7 +20407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 03:55 · W20 · 12-18 may 2026</t>
+          <t>Generado: 19/05/2026 04:09 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19508,7 +19508,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19927,7 +19927,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 19/05/2026 05:04 · W20 · 12-18 may 2026</t>
+          <t>Generado: 21/05/2026 22:18 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
+++ b/checkrates/week-20/Analisis_Checkrates_OP_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14056,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19508,7 +19508,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19927,7 +19927,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/05/2026 21:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 24/05/2026 21:49 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
